--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Allowed coded values for AnaliticsCodes, generated from enum_models.py.</t>
+    <t>Allowed coded values for AnaliticsCodes</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -9,12 +9,13 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="60">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -155,6 +156,45 @@
   </si>
   <si>
     <t>http://tecnomod-um.org/CodeSystem/analytics-codes-cs</t>
+  </si>
+  <si>
+    <t>hyperglycemia-day-1</t>
+  </si>
+  <si>
+    <t>Hyperglycemia Checks Day 1</t>
+  </si>
+  <si>
+    <t>hyperglycemia-day-2</t>
+  </si>
+  <si>
+    <t>Hyperglycemia Checks Day 2</t>
+  </si>
+  <si>
+    <t>hyperglycemia-day-3</t>
+  </si>
+  <si>
+    <t>Hyperglycemia Checks Day 3</t>
+  </si>
+  <si>
+    <t>temperature-checks-day-1</t>
+  </si>
+  <si>
+    <t>Temperature Checks Day 1</t>
+  </si>
+  <si>
+    <t>temperature-checks-day-2</t>
+  </si>
+  <si>
+    <t>Temperature Checks Day 2</t>
+  </si>
+  <si>
+    <t>temperature-checks-day-3</t>
+  </si>
+  <si>
+    <t>Temperature Checks Day 3</t>
+  </si>
+  <si>
+    <t>http://tecnomod-um.org/CodeSystem/timing-metric-codes-cs</t>
   </si>
 </sst>
 </file>
@@ -546,4 +586,90 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -26,7 +26,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/analitics-codes-vs</t>
+    <t>http://qualityregistry.org/ValueSet/analitics-codes-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -74,7 +74,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -155,7 +155,7 @@
     <t>Highest Hyperglycemia Value</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/CodeSystem/analytics-codes-cs</t>
+    <t>http://qualityregistry.org/CodeSystem/analytics-codes-cs</t>
   </si>
   <si>
     <t>hyperglycemia-day-1</t>
@@ -194,7 +194,7 @@
     <t>Temperature Checks Day 3</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/CodeSystem/timing-metric-codes-cs</t>
+    <t>http://qualityregistry.org/CodeSystem/timing-metric-codes-cs</t>
   </si>
 </sst>
 </file>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-analitics-codes-vs.xlsx
+++ b/ValueSet-analitics-codes-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
